--- a/car_detailing_valuation_model.xlsx
+++ b/car_detailing_valuation_model.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Revenue Projections" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Operating Expenses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="P&amp;L Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Scenario Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Financial Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Valuation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Scenario Analysis" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +49,12 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -69,12 +71,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F4F8"/>
         <bgColor rgb="00E8F4F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-        <bgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -136,24 +132,26 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -522,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -539,7 +537,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>UNIT ECONOMICS</t>
+          <t>UNIT ECONOMICS - PER-JOB REVENUE</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -589,202 +587,211 @@
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Gross Margin %</t>
-        </is>
-      </c>
-      <c r="B8" s="7">
-        <f>B7/B4</f>
-        <v/>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SUBSCRIPTION REVENUE</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>GROWTH ASSUMPTIONS (MONTHLY)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Monthly Subscription Price (per vehicle)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Month 1: Jobs per Day</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>5</v>
+          <t>Year 1: Starting Subscribers</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Operating Days per Month</t>
+          <t>Monthly Subscriber Growth Rate</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>20</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Monthly Job Growth Rate</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Projection Period (Years)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
+          <t>Churn Rate (monthly)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GROWTH ASSUMPTIONS (MONTHLY)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Month 1: Jobs per Day</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>ANNUAL PRICING &amp; VOLUME</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Annual Price Increase %</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>0.05</v>
+          <t>Operating Days per Month</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Year 2+ Location Expansion (# locations)</t>
+          <t>Monthly Job Growth Rate</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Annual Price Increase %</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>OPERATING COSTS (ANNUAL)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Rent (per location, annual)</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>24000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Utilities &amp; Insurance (per location)</t>
+          <t>Rent (per location, annual)</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>6000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Management Salary (Owner)</t>
+          <t>Utilities &amp; Insurance (per location)</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>50000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Marketing &amp; Customer Acquisition</t>
+          <t>Management Salary (Owner)</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>12000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>Marketing &amp; Customer Acquisition</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>Equipment &amp; Supplies (initial + maintenance)</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B26" s="4" t="n">
         <v>8000</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>FINANCING &amp; DISCOUNT RATE</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Initial Capital Required</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>50000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DCF Discount Rate (WACC)</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>0.1</v>
+          <t>Initial Capital Required</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>DCF Discount Rate (WACC)</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>Terminal Growth Rate</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B31" s="8" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -799,21 +806,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>REVENUE PROJECTIONS</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>5-YEAR FINANCIAL PROJECTIONS</t>
         </is>
       </c>
     </row>
@@ -849,187 +856,672 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t># of Locations</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Jobs per Day (per location, YE)</t>
-        </is>
-      </c>
-      <c r="B5" s="11">
-        <f>Assumptions!$B$11*(1+Assumptions!$B$13)^11</f>
-        <v/>
-      </c>
-      <c r="C5" s="11">
-        <f>B5*(1+Assumptions!$B$13)^12</f>
-        <v/>
-      </c>
-      <c r="D5" s="11">
-        <f>C5*(1+Assumptions!$B$13)^12</f>
-        <v/>
-      </c>
-      <c r="E5" s="11">
-        <f>D5*(1+Assumptions!$B$13)^12</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>E5*(1+Assumptions!$B$13)^12</f>
-        <v/>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Avg Jobs per Day (during year)</t>
+          <t>Jobs per Day (per location, YE)</t>
         </is>
       </c>
       <c r="B6" s="11">
-        <f>(Assumptions!$B$11 + B5) / 2</f>
+        <f>Assumptions!$B$16*(1+Assumptions!$B$18)^11</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>(B5 + C5) / 2</f>
+        <f>B6*(1+Assumptions!$B$18)^12</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>(C5 + D5) / 2</f>
+        <f>C6*(1+Assumptions!$B$18)^12</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>(D5 + E5) / 2</f>
+        <f>D6*(1+Assumptions!$B$18)^12</f>
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>(E5 + F5) / 2</f>
+        <f>E6*(1+Assumptions!$B$18)^12</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Operating Days per Year</t>
+          <t>Avg Jobs per Day (during year)</t>
         </is>
       </c>
       <c r="B7" s="11">
-        <f>$B$7</f>
+        <f>(Assumptions!$B$16 + B6) / 2</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>$B$7</f>
+        <f>(B6 + C6) / 2</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>$B$7</f>
+        <f>(C6 + D6) / 2</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>$B$7</f>
+        <f>(D6 + E6) / 2</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>$B$7</f>
+        <f>(E6 + F6) / 2</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total Jobs per Year</t>
+          <t>Operating Days per Year</t>
         </is>
       </c>
       <c r="B8" s="11">
-        <f>B4*B6*B7</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>C4*C6*C7</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>D4*D6*D7</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>E4*E6*E7</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="F8" s="11">
-        <f>F4*F6*F7</f>
+        <f>$B$8</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARPD</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Assumptions!$B$4</f>
-        <v/>
-      </c>
-      <c r="C9" s="6">
-        <f>B9*(1+Assumptions!$B$17)</f>
-        <v/>
-      </c>
-      <c r="D9" s="6">
-        <f>C9*(1+Assumptions!$B$17)</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>D9*(1+Assumptions!$B$17)</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>E9*(1+Assumptions!$B$17)</f>
+          <t>Total Jobs per Year</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>B7*B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>C7*C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>D7*D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>E7*E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="11">
+        <f>F7*F8</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B10" s="12">
-        <f>B8*B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="12">
-        <f>C8*C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="12">
-        <f>D8*D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="12">
-        <f>E8*E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
-        <f>F8*F9</f>
+          <t>ARPD</t>
+        </is>
+      </c>
+      <c r="B10" s="6">
+        <f>Assumptions!$B$4</f>
+        <v/>
+      </c>
+      <c r="C10" s="6">
+        <f>B10*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="D10" s="6">
+        <f>C10*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="E10" s="6">
+        <f>D10*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="F10" s="6">
+        <f>E10*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Per-Job Revenue</t>
+        </is>
+      </c>
+      <c r="B11" s="6">
+        <f>B9*B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="6">
+        <f>C9*C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="6">
+        <f>D9*D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="6">
+        <f>E9*E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="6">
+        <f>F9*F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Subscribers (YE)</t>
+        </is>
+      </c>
+      <c r="B13" s="11">
+        <f>Assumptions!$B$11*(1+Assumptions!$B$12)^11*(1-Assumptions!$B$13)^11</f>
+        <v/>
+      </c>
+      <c r="C13" s="11">
+        <f>B13*(1+Assumptions!$B$12)^12*(1-Assumptions!$B$13)^12</f>
+        <v/>
+      </c>
+      <c r="D13" s="11">
+        <f>C13*(1+Assumptions!$B$12)^12*(1-Assumptions!$B$13)^12</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>D13*(1+Assumptions!$B$12)^12*(1-Assumptions!$B$13)^12</f>
+        <v/>
+      </c>
+      <c r="F13" s="11">
+        <f>E13*(1+Assumptions!$B$12)^12*(1-Assumptions!$B$13)^12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Avg Subscribers (during year)</t>
+        </is>
+      </c>
+      <c r="B14" s="11">
+        <f>(Assumptions!$B$11 + B13) / 2</f>
+        <v/>
+      </c>
+      <c r="C14" s="11">
+        <f>(B13 + C13) / 2</f>
+        <v/>
+      </c>
+      <c r="D14" s="11">
+        <f>(C13 + D13) / 2</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>(D13 + E13) / 2</f>
+        <v/>
+      </c>
+      <c r="F14" s="11">
+        <f>(E13 + F13) / 2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Monthly Subscription Price</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>Assumptions!$B$10</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>B15*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>C15*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>D15*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="F15" s="6">
+        <f>E15*(1+Assumptions!$B$19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Subscription Revenue (Annual)</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
+        <f>B14*B15*12</f>
+        <v/>
+      </c>
+      <c r="C16" s="6">
+        <f>C14*C15*12</f>
+        <v/>
+      </c>
+      <c r="D16" s="6">
+        <f>D14*D15*12</f>
+        <v/>
+      </c>
+      <c r="E16" s="6">
+        <f>E14*E15*12</f>
+        <v/>
+      </c>
+      <c r="F16" s="6">
+        <f>F14*F15*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>B11+B16</f>
+        <v/>
+      </c>
+      <c r="C18" s="12">
+        <f>C11+C16</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>D11+D16</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>E11+E16</f>
+        <v/>
+      </c>
+      <c r="F18" s="12">
+        <f>F11+F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>COSTS OF GOODS SOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Materials &amp; Supplies Cost</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <f>B9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="C21" s="6">
+        <f>C9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="D21" s="6">
+        <f>D9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E21" s="6">
+        <f>E9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="F21" s="6">
+        <f>F9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Labor Cost</t>
+        </is>
+      </c>
+      <c r="B22" s="6">
+        <f>B9*Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="C22" s="6">
+        <f>C9*Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="D22" s="6">
+        <f>D9*Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="E22" s="6">
+        <f>E9*Assumptions!$B$6</f>
+        <v/>
+      </c>
+      <c r="F22" s="6">
+        <f>F9*Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total COGS</t>
+        </is>
+      </c>
+      <c r="B23" s="13">
+        <f>B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="13">
+        <f>C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="13">
+        <f>D21+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="13">
+        <f>E21+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="13">
+        <f>F21+F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <f>B18-B23</f>
+        <v/>
+      </c>
+      <c r="C25" s="6">
+        <f>C18-C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="6">
+        <f>D18-D23</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
+        <f>E18-E23</f>
+        <v/>
+      </c>
+      <c r="F25" s="6">
+        <f>F18-F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="B26" s="14">
+        <f>B25/B18</f>
+        <v/>
+      </c>
+      <c r="C26" s="14">
+        <f>C25/C18</f>
+        <v/>
+      </c>
+      <c r="D26" s="14">
+        <f>D25/D18</f>
+        <v/>
+      </c>
+      <c r="E26" s="14">
+        <f>E25/E18</f>
+        <v/>
+      </c>
+      <c r="F26" s="14">
+        <f>F25/F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="B29" s="6">
+        <f>Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="C29" s="6">
+        <f>Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="D29" s="6">
+        <f>Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="E29" s="6">
+        <f>Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="F29" s="6">
+        <f>Assumptions!$B$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="B30" s="6">
+        <f>Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="C30" s="6">
+        <f>Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="D30" s="6">
+        <f>Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="E30" s="6">
+        <f>Assumptions!$B$23</f>
+        <v/>
+      </c>
+      <c r="F30" s="6">
+        <f>Assumptions!$B$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Management Salary</t>
+        </is>
+      </c>
+      <c r="B31" s="6">
+        <f>Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="C31" s="6">
+        <f>Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="D31" s="6">
+        <f>Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="E31" s="6">
+        <f>Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="F31" s="6">
+        <f>Assumptions!$B$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Customer Acquisition</t>
+        </is>
+      </c>
+      <c r="B32" s="6">
+        <f>Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="C32" s="6">
+        <f>Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="D32" s="6">
+        <f>Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="E32" s="6">
+        <f>Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="F32" s="6">
+        <f>Assumptions!$B$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Equipment &amp; Supplies</t>
+        </is>
+      </c>
+      <c r="B33" s="6">
+        <f>Assumptions!$B$26</f>
+        <v/>
+      </c>
+      <c r="C33" s="6">
+        <f>Assumptions!$B$26</f>
+        <v/>
+      </c>
+      <c r="D33" s="6">
+        <f>Assumptions!$B$26</f>
+        <v/>
+      </c>
+      <c r="E33" s="6">
+        <f>Assumptions!$B$26</f>
+        <v/>
+      </c>
+      <c r="F33" s="6">
+        <f>Assumptions!$B$26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B34" s="13">
+        <f>B29+B30+B31+B32+B33</f>
+        <v/>
+      </c>
+      <c r="C34" s="13">
+        <f>C29+C30+C31+C32+C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="13">
+        <f>D29+D30+D31+D32+D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="13">
+        <f>E29+E30+E31+E32+E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="13">
+        <f>F29+F30+F31+F32+F33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B36" s="15">
+        <f>B25-B34</f>
+        <v/>
+      </c>
+      <c r="C36" s="15">
+        <f>C25-C34</f>
+        <v/>
+      </c>
+      <c r="D36" s="15">
+        <f>D25-D34</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
+        <f>E25-E34</f>
+        <v/>
+      </c>
+      <c r="F36" s="15">
+        <f>F25-F34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EBITDA Margin %</t>
+        </is>
+      </c>
+      <c r="B37" s="14">
+        <f>B36/B18</f>
+        <v/>
+      </c>
+      <c r="C37" s="14">
+        <f>C36/C18</f>
+        <v/>
+      </c>
+      <c r="D37" s="14">
+        <f>D36/D18</f>
+        <v/>
+      </c>
+      <c r="E37" s="14">
+        <f>E36/E18</f>
+        <v/>
+      </c>
+      <c r="F37" s="14">
+        <f>F36/F18</f>
         <v/>
       </c>
     </row>
@@ -1039,574 +1531,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>OPERATING EXPENSES</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>COGS - VARIABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Materials &amp; Supplies Cost</t>
-        </is>
-      </c>
-      <c r="B5" s="6">
-        <f>'Revenue Projections'!B8*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="C5" s="6">
-        <f>'Revenue Projections'!C8*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="D5" s="6">
-        <f>'Revenue Projections'!D8*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E5" s="6">
-        <f>'Revenue Projections'!E8*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="F5" s="6">
-        <f>'Revenue Projections'!F8*Assumptions!$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Labor Cost</t>
-        </is>
-      </c>
-      <c r="B6" s="6">
-        <f>'Revenue Projections'!B8*Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="C6" s="6">
-        <f>'Revenue Projections'!C8*Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="6">
-        <f>'Revenue Projections'!D8*Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="6">
-        <f>'Revenue Projections'!E8*Assumptions!$B$6</f>
-        <v/>
-      </c>
-      <c r="F6" s="6">
-        <f>'Revenue Projections'!F8*Assumptions!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total COGS</t>
-        </is>
-      </c>
-      <c r="B7" s="13">
-        <f>B5+B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="13">
-        <f>C5+C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>D5+D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>E5+E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>F5+F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FIXED OPERATING EXPENSES</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Rent (per location)</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>'Revenue Projections'!B4*Assumptions!$B$21</f>
-        <v/>
-      </c>
-      <c r="C10" s="6">
-        <f>'Revenue Projections'!C4*Assumptions!$B$21</f>
-        <v/>
-      </c>
-      <c r="D10" s="6">
-        <f>'Revenue Projections'!D4*Assumptions!$B$21</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>'Revenue Projections'!E4*Assumptions!$B$21</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>'Revenue Projections'!F4*Assumptions!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Utilities &amp; Insurance</t>
-        </is>
-      </c>
-      <c r="B11" s="6">
-        <f>'Revenue Projections'!B4*Assumptions!$B$22</f>
-        <v/>
-      </c>
-      <c r="C11" s="6">
-        <f>'Revenue Projections'!C4*Assumptions!$B$22</f>
-        <v/>
-      </c>
-      <c r="D11" s="6">
-        <f>'Revenue Projections'!D4*Assumptions!$B$22</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>'Revenue Projections'!E4*Assumptions!$B$22</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>'Revenue Projections'!F4*Assumptions!$B$22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Management Salary</t>
-        </is>
-      </c>
-      <c r="B12" s="6">
-        <f>Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="C12" s="6">
-        <f>Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="D12" s="6">
-        <f>Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>Assumptions!$B$23</f>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f>Assumptions!$B$23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Customer Acquisition</t>
-        </is>
-      </c>
-      <c r="B13" s="6">
-        <f>Assumptions!$B$24</f>
-        <v/>
-      </c>
-      <c r="C13" s="6">
-        <f>Assumptions!$B$24</f>
-        <v/>
-      </c>
-      <c r="D13" s="6">
-        <f>Assumptions!$B$24</f>
-        <v/>
-      </c>
-      <c r="E13" s="6">
-        <f>Assumptions!$B$24</f>
-        <v/>
-      </c>
-      <c r="F13" s="6">
-        <f>Assumptions!$B$24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Equipment &amp; Supplies</t>
-        </is>
-      </c>
-      <c r="B14" s="6">
-        <f>Assumptions!$B$25</f>
-        <v/>
-      </c>
-      <c r="C14" s="6">
-        <f>Assumptions!$B$25</f>
-        <v/>
-      </c>
-      <c r="D14" s="6">
-        <f>Assumptions!$B$25</f>
-        <v/>
-      </c>
-      <c r="E14" s="6">
-        <f>Assumptions!$B$25</f>
-        <v/>
-      </c>
-      <c r="F14" s="6">
-        <f>Assumptions!$B$25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Total Fixed Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B15" s="13">
-        <f>B10+B11+B12+B13+B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="13">
-        <f>C10+C11+C12+C13+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="13">
-        <f>D10+D11+D12+D13+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="13">
-        <f>E10+E11+E12+E13+E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="13">
-        <f>F10+F11+F12+F13+F14</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>PROFIT &amp; LOSS SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Year 1</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Year 2</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Year 3</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Year 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B4" s="12">
-        <f>'Revenue Projections'!B10</f>
-        <v/>
-      </c>
-      <c r="C4" s="12">
-        <f>'Revenue Projections'!C10</f>
-        <v/>
-      </c>
-      <c r="D4" s="12">
-        <f>'Revenue Projections'!D10</f>
-        <v/>
-      </c>
-      <c r="E4" s="12">
-        <f>'Revenue Projections'!E10</f>
-        <v/>
-      </c>
-      <c r="F4" s="12">
-        <f>'Revenue Projections'!F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="B5" s="6">
-        <f>'Operating Expenses'!B7</f>
-        <v/>
-      </c>
-      <c r="C5" s="6">
-        <f>'Operating Expenses'!C7</f>
-        <v/>
-      </c>
-      <c r="D5" s="6">
-        <f>'Operating Expenses'!D7</f>
-        <v/>
-      </c>
-      <c r="E5" s="6">
-        <f>'Operating Expenses'!E7</f>
-        <v/>
-      </c>
-      <c r="F5" s="6">
-        <f>'Operating Expenses'!F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B6" s="14">
-        <f>B4-B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="14">
-        <f>C4-C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="14">
-        <f>D4-D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="14">
-        <f>E4-E5</f>
-        <v/>
-      </c>
-      <c r="F6" s="14">
-        <f>F4-F5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gross Margin %</t>
-        </is>
-      </c>
-      <c r="B7" s="7">
-        <f>B6/B4</f>
-        <v/>
-      </c>
-      <c r="C7" s="7">
-        <f>C6/C4</f>
-        <v/>
-      </c>
-      <c r="D7" s="7">
-        <f>D6/D4</f>
-        <v/>
-      </c>
-      <c r="E7" s="7">
-        <f>E6/E4</f>
-        <v/>
-      </c>
-      <c r="F7" s="7">
-        <f>F6/F4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>'Operating Expenses'!B15</f>
-        <v/>
-      </c>
-      <c r="C9" s="6">
-        <f>'Operating Expenses'!C15</f>
-        <v/>
-      </c>
-      <c r="D9" s="6">
-        <f>'Operating Expenses'!D15</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>'Operating Expenses'!E15</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>'Operating Expenses'!F15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B10" s="15">
-        <f>B6-B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="15">
-        <f>C6-C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="15">
-        <f>D6-D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="15">
-        <f>E6-E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="15">
-        <f>F6-F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EBITDA Margin %</t>
-        </is>
-      </c>
-      <c r="B11" s="7">
-        <f>B10/B4</f>
-        <v/>
-      </c>
-      <c r="C11" s="7">
-        <f>C10/C4</f>
-        <v/>
-      </c>
-      <c r="D11" s="7">
-        <f>D10/D4</f>
-        <v/>
-      </c>
-      <c r="E11" s="7">
-        <f>E10/E4</f>
-        <v/>
-      </c>
-      <c r="F11" s="7">
-        <f>F10/F4</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1620,7 +1544,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ENTERPRISE VALUATION</t>
         </is>
@@ -1673,23 +1597,23 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>'P&amp;L Summary'!B10</f>
+        <f>'Financial Model'!B36</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>'P&amp;L Summary'!C10</f>
+        <f>'Financial Model'!C36</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>'P&amp;L Summary'!D10</f>
+        <f>'Financial Model'!D36</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>'P&amp;L Summary'!E10</f>
+        <f>'Financial Model'!E36</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>'P&amp;L Summary'!F10</f>
+        <f>'Financial Model'!F36</f>
         <v/>
       </c>
     </row>
@@ -1726,23 +1650,23 @@
           <t>NOPAT (Net Operating Profit)</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="17">
         <f>B6-B7</f>
         <v/>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="17">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="17">
         <f>D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="17">
         <f>E6-E7</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="17">
         <f>F6-F7</f>
         <v/>
       </c>
@@ -1753,24 +1677,24 @@
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>1/(1+Assumptions!$B$29)^1</f>
-        <v/>
-      </c>
-      <c r="C9" s="7">
-        <f>1/(1+Assumptions!$B$29)^2</f>
-        <v/>
-      </c>
-      <c r="D9" s="7">
-        <f>1/(1+Assumptions!$B$29)^3</f>
-        <v/>
-      </c>
-      <c r="E9" s="7">
-        <f>1/(1+Assumptions!$B$29)^4</f>
-        <v/>
-      </c>
-      <c r="F9" s="7">
-        <f>1/(1+Assumptions!$B$29)^5</f>
+      <c r="B9" s="14">
+        <f>1/(1+Assumptions!$B$30)^1</f>
+        <v/>
+      </c>
+      <c r="C9" s="14">
+        <f>1/(1+Assumptions!$B$30)^2</f>
+        <v/>
+      </c>
+      <c r="D9" s="14">
+        <f>1/(1+Assumptions!$B$30)^3</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>1/(1+Assumptions!$B$30)^4</f>
+        <v/>
+      </c>
+      <c r="F9" s="14">
+        <f>1/(1+Assumptions!$B$30)^5</f>
         <v/>
       </c>
     </row>
@@ -1780,23 +1704,23 @@
           <t>PV of Cash Flows</t>
         </is>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="17">
         <f>B8*B9</f>
         <v/>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="17">
         <f>C8*C9</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="17">
         <f>D8*D9</f>
         <v/>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="17">
         <f>E8*E9</f>
         <v/>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="17">
         <f>F8*F9</f>
         <v/>
       </c>
@@ -1807,7 +1731,7 @@
           <t>Sum of PV (5 Years)</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="18">
         <f>SUM(B10:F10)</f>
         <v/>
       </c>
@@ -1818,7 +1742,7 @@
           <t>Terminal Value (NOPAT Year 5 * 8x EBITDA multiple)</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <f>F8*8</f>
         <v/>
       </c>
@@ -1829,7 +1753,7 @@
           <t>PV of Terminal Value</t>
         </is>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="18">
         <f>B13*F9</f>
         <v/>
       </c>
@@ -1840,7 +1764,7 @@
           <t>ENTERPRISE VALUE (DCF)</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>B12+B14</f>
         <v/>
       </c>
@@ -1864,7 +1788,7 @@
         </is>
       </c>
       <c r="B20" s="6">
-        <f>'P&amp;L Summary'!F4</f>
+        <f>'Financial Model'!F18</f>
         <v/>
       </c>
     </row>
@@ -1874,7 +1798,7 @@
           <t>Revenue Multiple (3.5x)</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="21" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -1896,7 +1820,7 @@
         </is>
       </c>
       <c r="B24" s="6">
-        <f>'P&amp;L Summary'!F10</f>
+        <f>'Financial Model'!F36</f>
         <v/>
       </c>
     </row>
@@ -1906,7 +1830,7 @@
           <t>EBITDA Multiple (6.0x)</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1922,12 +1846,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>VALUATION SUMMARY</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
+      <c r="B28" s="22" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1935,7 +1859,7 @@
           <t>DCF Valuation</t>
         </is>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="17">
         <f>B16</f>
         <v/>
       </c>
@@ -1968,7 +1892,7 @@
           <t>Average Valuation</t>
         </is>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="23">
         <f>AVERAGE(B29:B31)</f>
         <v/>
       </c>
@@ -1978,7 +1902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1995,7 +1919,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>SCENARIO ANALYSIS - YEAR 5 PERFORMANCE</t>
         </is>
@@ -2034,20 +1958,20 @@
           <t>BASE CASE</t>
         </is>
       </c>
-      <c r="B4" s="23">
-        <f>Assumptions!$B$13</f>
-        <v/>
-      </c>
-      <c r="C4" s="12">
-        <f>'P&amp;L Summary'!F4</f>
-        <v/>
-      </c>
-      <c r="D4" s="12">
-        <f>'P&amp;L Summary'!F10</f>
-        <v/>
-      </c>
-      <c r="E4" s="12">
-        <f>'P&amp;L Summary'!F11</f>
+      <c r="B4" s="24">
+        <f>Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="C4" s="25">
+        <f>'Financial Model'!F18</f>
+        <v/>
+      </c>
+      <c r="D4" s="25">
+        <f>'Financial Model'!F36</f>
+        <v/>
+      </c>
+      <c r="E4" s="24">
+        <f>'Financial Model'!F37</f>
         <v/>
       </c>
     </row>
@@ -2057,12 +1981,12 @@
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2070,22 +1994,22 @@
           <t>OPTIMISTIC</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>0.12</v>
       </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>INSTRUCTIONS:</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Update the Monthly Growth rates for Conservative (5%) and Optimistic (12%) scenarios, and the model will recalculate all values in the yellow cells.</t>
         </is>
